--- a/Config/Excel/GameConfig/SkillEffectConfig.xlsx
+++ b/Config/Excel/GameConfig/SkillEffectConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,10 +630,315 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>基础物理伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>51011</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>999999</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>玩家割草版物理伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>52001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>冻结0.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>52002</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>冻结1秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>52003</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>冻结1.5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>52004</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>冻结2秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>52005</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>冻结3秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>53001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>击退1米</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>53002</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>击退2米</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>53003</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>击退3米</t>
         </is>
       </c>
     </row>
